--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515908</v>
+        <v>122515717</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518791</v>
+        <v>519373</v>
       </c>
       <c r="R2" t="n">
-        <v>7056375</v>
+        <v>7056175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516142</v>
+        <v>122516490</v>
       </c>
       <c r="B3" t="n">
         <v>78652</v>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519227</v>
+        <v>519147</v>
       </c>
       <c r="R3" t="n">
-        <v>7056195</v>
+        <v>7056252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515717</v>
+        <v>122515908</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,11 +940,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519373</v>
+        <v>518791</v>
       </c>
       <c r="R4" t="n">
-        <v>7056175</v>
+        <v>7056375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,26 +1015,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1026,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515390</v>
+        <v>122514876</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519241</v>
+        <v>519221</v>
       </c>
       <c r="R5" t="n">
-        <v>7056163</v>
+        <v>7056184</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,31 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122514876</v>
+        <v>122515545</v>
       </c>
       <c r="B6" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1144,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519221</v>
+        <v>519292</v>
       </c>
       <c r="R6" t="n">
-        <v>7056184</v>
+        <v>7056181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,6 +1209,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122516799</v>
+        <v>122515980</v>
       </c>
       <c r="B7" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,22 +1261,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519073</v>
+        <v>519364</v>
       </c>
       <c r="R7" t="n">
-        <v>7056218</v>
+        <v>7056189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,6 +1326,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122515545</v>
+        <v>122516799</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,29 +1525,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519292</v>
+        <v>519073</v>
       </c>
       <c r="R9" t="n">
-        <v>7056181</v>
+        <v>7056218</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,12 +1608,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1626,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515626</v>
+        <v>122516358</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,22 +1647,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518946</v>
+        <v>519177</v>
       </c>
       <c r="R10" t="n">
-        <v>7056283</v>
+        <v>7056244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1717,6 +1717,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1733,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516358</v>
+        <v>122516142</v>
       </c>
       <c r="B11" t="n">
-        <v>90831</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,34 +1769,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519177</v>
+        <v>519227</v>
       </c>
       <c r="R11" t="n">
-        <v>7056244</v>
+        <v>7056195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,12 +1847,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1855,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122516661</v>
+        <v>122515626</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1889,21 +1904,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519111</v>
+        <v>518946</v>
       </c>
       <c r="R12" t="n">
-        <v>7056260</v>
+        <v>7056283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1950,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på stambasen av en gammal gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,26 +1961,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1987,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515980</v>
+        <v>122516432</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,11 +1993,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2032,13 +2022,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519364</v>
+        <v>519181</v>
       </c>
       <c r="R13" t="n">
-        <v>7056189</v>
+        <v>7056245</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2072,7 +2062,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516432</v>
+        <v>122515390</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,39 +2125,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519181</v>
+        <v>519241</v>
       </c>
       <c r="R14" t="n">
-        <v>7056245</v>
+        <v>7056163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,11 +2182,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2228,12 +2203,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2251,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122516490</v>
+        <v>122516661</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,29 +2242,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519147</v>
+        <v>519111</v>
       </c>
       <c r="R15" t="n">
-        <v>7056252</v>
+        <v>7056260</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,7 +2311,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Tydliga äldre ringhack på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,12 +2335,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515717</v>
+        <v>122516142</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519373</v>
+        <v>519227</v>
       </c>
       <c r="R2" t="n">
-        <v>7056175</v>
+        <v>7056195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,6 +767,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516490</v>
+        <v>122514876</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519147</v>
+        <v>519221</v>
       </c>
       <c r="R3" t="n">
-        <v>7056252</v>
+        <v>7056184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,11 +880,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,26 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515908</v>
+        <v>122515980</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,6 +922,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -958,19 +943,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518791</v>
+        <v>519364</v>
       </c>
       <c r="R4" t="n">
-        <v>7056375</v>
+        <v>7056189</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,6 +1005,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122514876</v>
+        <v>122516432</v>
       </c>
       <c r="B5" t="n">
-        <v>90831</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,29 +1062,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519221</v>
+        <v>519181</v>
       </c>
       <c r="R5" t="n">
-        <v>7056184</v>
+        <v>7056245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1134,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1112,6 +1147,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515545</v>
+        <v>122515359</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,29 +1204,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519292</v>
+        <v>519258</v>
       </c>
       <c r="R6" t="n">
-        <v>7056181</v>
+        <v>7056164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,6 +1276,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1215,6 +1295,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1222,12 +1307,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1245,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515980</v>
+        <v>122515717</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,11 +1346,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1279,24 +1369,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519364</v>
+        <v>519373</v>
       </c>
       <c r="R7" t="n">
-        <v>7056189</v>
+        <v>7056175</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1415,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,6 +1432,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1354,12 +1444,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1377,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122515359</v>
+        <v>122516358</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,27 +1483,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1512,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519258</v>
+        <v>519177</v>
       </c>
       <c r="R8" t="n">
-        <v>7056164</v>
+        <v>7056244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,11 +1550,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1479,6 +1564,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1486,12 +1576,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1509,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122516799</v>
+        <v>122515908</v>
       </c>
       <c r="B9" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,22 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,10 +1644,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519073</v>
+        <v>518791</v>
       </c>
       <c r="R9" t="n">
-        <v>7056218</v>
+        <v>7056375</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,6 +1682,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1595,26 +1695,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,10 +1711,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122516358</v>
+        <v>122515390</v>
       </c>
       <c r="B10" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,34 +1727,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519177</v>
+        <v>519241</v>
       </c>
       <c r="R10" t="n">
-        <v>7056244</v>
+        <v>7056163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,6 +1803,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1730,12 +1815,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1753,10 +1838,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516142</v>
+        <v>122516490</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,6 +1856,11 @@
       <c r="E11" t="n">
         <v>6425</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1788,10 +1878,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519227</v>
+        <v>519147</v>
       </c>
       <c r="R11" t="n">
-        <v>7056195</v>
+        <v>7056252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1916,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1838,6 +1933,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1873,7 +1973,7 @@
         <v>122515626</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,6 +1987,11 @@
       </c>
       <c r="E12" t="n">
         <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1977,10 +2082,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122516432</v>
+        <v>122515545</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,39 +2098,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519181</v>
+        <v>519292</v>
       </c>
       <c r="R13" t="n">
-        <v>7056245</v>
+        <v>7056181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,11 +2160,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2079,6 +2174,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2086,12 +2186,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2109,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515390</v>
+        <v>122516799</v>
       </c>
       <c r="B14" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,29 +2225,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519241</v>
+        <v>519073</v>
       </c>
       <c r="R14" t="n">
-        <v>7056163</v>
+        <v>7056218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,6 +2306,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2203,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2229,7 +2344,7 @@
         <v>122516661</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,6 +2359,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2326,6 +2446,11 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122516142</v>
+        <v>122515545</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519227</v>
+        <v>519292</v>
       </c>
       <c r="R2" t="n">
-        <v>7056195</v>
+        <v>7056181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514876</v>
+        <v>122515359</v>
       </c>
       <c r="B3" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519221</v>
+        <v>519258</v>
       </c>
       <c r="R3" t="n">
-        <v>7056184</v>
+        <v>7056164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +890,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,6 +903,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515980</v>
+        <v>122516799</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,32 +960,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519364</v>
+        <v>519073</v>
       </c>
       <c r="R4" t="n">
-        <v>7056189</v>
+        <v>7056218</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,11 +1025,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122516432</v>
+        <v>122516490</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,44 +1092,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519181</v>
+        <v>519147</v>
       </c>
       <c r="R5" t="n">
-        <v>7056245</v>
+        <v>7056252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1156,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,12 +1185,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1188,10 +1208,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515359</v>
+        <v>122515390</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,44 +1224,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519258</v>
+        <v>519241</v>
       </c>
       <c r="R6" t="n">
-        <v>7056164</v>
+        <v>7056163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,11 +1286,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,12 +1312,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515717</v>
+        <v>122516142</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,39 +1351,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519373</v>
+        <v>519227</v>
       </c>
       <c r="R7" t="n">
-        <v>7056175</v>
+        <v>7056195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,11 +1413,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1444,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122516358</v>
+        <v>122514876</v>
       </c>
       <c r="B8" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,21 +1496,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519177</v>
+        <v>519221</v>
       </c>
       <c r="R8" t="n">
-        <v>7056244</v>
+        <v>7056184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,31 +1548,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1711,10 +1676,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515390</v>
+        <v>122515717</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,34 +1692,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519241</v>
+        <v>519373</v>
       </c>
       <c r="R10" t="n">
-        <v>7056163</v>
+        <v>7056175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,6 +1759,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1815,12 +1790,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1838,10 +1813,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516490</v>
+        <v>122515626</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1854,34 +1829,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519147</v>
+        <v>518946</v>
       </c>
       <c r="R11" t="n">
-        <v>7056252</v>
+        <v>7056283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1918,7 +1898,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,31 +1909,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1970,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515626</v>
+        <v>122516358</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1986,27 +1941,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2015,10 +1970,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518946</v>
+        <v>519177</v>
       </c>
       <c r="R12" t="n">
-        <v>7056283</v>
+        <v>7056244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2053,11 +2008,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2066,6 +2016,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2082,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515545</v>
+        <v>122515980</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2098,37 +2073,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519292</v>
+        <v>519364</v>
       </c>
       <c r="R13" t="n">
-        <v>7056181</v>
+        <v>7056189</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,6 +2145,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2186,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2209,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516799</v>
+        <v>122516432</v>
       </c>
       <c r="B14" t="n">
-        <v>90844</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2225,27 +2215,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519073</v>
+        <v>519181</v>
       </c>
       <c r="R14" t="n">
-        <v>7056218</v>
+        <v>7056245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2290,6 +2285,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515545</v>
+        <v>122515908</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519292</v>
+        <v>518791</v>
       </c>
       <c r="R2" t="n">
-        <v>7056181</v>
+        <v>7056375</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,31 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515359</v>
+        <v>122515717</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,12 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519258</v>
+        <v>519373</v>
       </c>
       <c r="R3" t="n">
-        <v>7056164</v>
+        <v>7056175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122516799</v>
+        <v>122515545</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519073</v>
+        <v>519292</v>
       </c>
       <c r="R4" t="n">
-        <v>7056218</v>
+        <v>7056181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1053,12 +1028,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122516490</v>
+        <v>122515390</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1116,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519147</v>
+        <v>519241</v>
       </c>
       <c r="R5" t="n">
-        <v>7056252</v>
+        <v>7056163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,11 +1127,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515390</v>
+        <v>122515626</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519241</v>
+        <v>518946</v>
       </c>
       <c r="R6" t="n">
-        <v>7056163</v>
+        <v>7056283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1261,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1294,31 +1274,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1335,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122516142</v>
+        <v>122515980</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,37 +1306,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519227</v>
+        <v>519364</v>
       </c>
       <c r="R7" t="n">
-        <v>7056195</v>
+        <v>7056189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1413,6 +1378,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1439,12 +1409,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514876</v>
+        <v>122516490</v>
       </c>
       <c r="B8" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,21 +1448,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1502,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519221</v>
+        <v>519147</v>
       </c>
       <c r="R8" t="n">
-        <v>7056184</v>
+        <v>7056252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,6 +1510,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1548,6 +1523,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1564,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122515908</v>
+        <v>122516142</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,39 +1580,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518791</v>
+        <v>519227</v>
       </c>
       <c r="R9" t="n">
-        <v>7056375</v>
+        <v>7056195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,11 +1642,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1660,6 +1650,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1676,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515717</v>
+        <v>122514876</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,39 +1707,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519373</v>
+        <v>519221</v>
       </c>
       <c r="R10" t="n">
-        <v>7056175</v>
+        <v>7056184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,11 +1769,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1772,31 +1777,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1813,10 +1793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515626</v>
+        <v>122516432</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1829,16 +1809,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1852,16 +1832,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518946</v>
+        <v>519181</v>
       </c>
       <c r="R11" t="n">
-        <v>7056283</v>
+        <v>7056245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1898,7 +1883,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,6 +1894,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1925,7 +1935,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122516358</v>
+        <v>122516799</v>
       </c>
       <c r="B12" t="n">
         <v>90857</v>
@@ -1970,10 +1980,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519177</v>
+        <v>519073</v>
       </c>
       <c r="R12" t="n">
-        <v>7056244</v>
+        <v>7056218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2057,7 +2067,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515980</v>
+        <v>122515359</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2093,7 +2103,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2107,13 +2117,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519364</v>
+        <v>519258</v>
       </c>
       <c r="R13" t="n">
-        <v>7056189</v>
+        <v>7056164</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2147,7 +2157,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,12 +2186,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2199,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516432</v>
+        <v>122516358</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>90857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,32 +2225,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519181</v>
+        <v>519177</v>
       </c>
       <c r="R14" t="n">
-        <v>7056245</v>
+        <v>7056244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,11 +2290,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515359</v>
+        <v>122516358</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2083,32 +2083,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519258</v>
+        <v>519177</v>
       </c>
       <c r="R13" t="n">
-        <v>7056164</v>
+        <v>7056244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2155,11 +2150,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2186,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2209,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516358</v>
+        <v>122515359</v>
       </c>
       <c r="B14" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2225,27 +2215,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519177</v>
+        <v>519258</v>
       </c>
       <c r="R14" t="n">
-        <v>7056244</v>
+        <v>7056164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,6 +2287,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515908</v>
+        <v>122516142</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518791</v>
+        <v>519227</v>
       </c>
       <c r="R2" t="n">
-        <v>7056375</v>
+        <v>7056195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515717</v>
+        <v>122516432</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -826,16 +841,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519373</v>
+        <v>519181</v>
       </c>
       <c r="R3" t="n">
-        <v>7056175</v>
+        <v>7056245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515545</v>
+        <v>122515980</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,37 +960,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519292</v>
+        <v>519364</v>
       </c>
       <c r="R4" t="n">
-        <v>7056181</v>
+        <v>7056189</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,6 +1032,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1028,12 +1063,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515390</v>
+        <v>122515908</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,34 +1102,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519241</v>
+        <v>518791</v>
       </c>
       <c r="R5" t="n">
-        <v>7056163</v>
+        <v>7056375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,6 +1169,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,31 +1182,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1178,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515626</v>
+        <v>122516358</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,27 +1214,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518946</v>
+        <v>519177</v>
       </c>
       <c r="R6" t="n">
-        <v>7056283</v>
+        <v>7056244</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,11 +1281,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,6 +1289,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,7 +1330,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515980</v>
+        <v>122515359</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1326,7 +1366,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1340,13 +1380,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519364</v>
+        <v>519258</v>
       </c>
       <c r="R7" t="n">
-        <v>7056189</v>
+        <v>7056164</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,12 +1449,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1564,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122516142</v>
+        <v>122515717</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,34 +1620,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519227</v>
+        <v>519373</v>
       </c>
       <c r="R9" t="n">
-        <v>7056195</v>
+        <v>7056175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1642,6 +1687,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1668,12 +1718,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1694,7 +1744,7 @@
         <v>122514876</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1793,10 +1843,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516432</v>
+        <v>122516799</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,32 +1859,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1843,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519181</v>
+        <v>519073</v>
       </c>
       <c r="R11" t="n">
-        <v>7056245</v>
+        <v>7056218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,11 +1924,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,10 +1975,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122516799</v>
+        <v>122515626</v>
       </c>
       <c r="B12" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,27 +1991,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1980,10 +2020,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519073</v>
+        <v>518946</v>
       </c>
       <c r="R12" t="n">
-        <v>7056218</v>
+        <v>7056283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,6 +2058,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2026,31 +2071,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2067,10 +2087,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122516358</v>
+        <v>122515545</v>
       </c>
       <c r="B13" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2083,39 +2103,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519177</v>
+        <v>519292</v>
       </c>
       <c r="R13" t="n">
-        <v>7056244</v>
+        <v>7056181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,12 +2191,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2199,10 +2214,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515359</v>
+        <v>122515390</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,44 +2230,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519258</v>
+        <v>519241</v>
       </c>
       <c r="R14" t="n">
-        <v>7056164</v>
+        <v>7056163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,11 +2292,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122516142</v>
+        <v>122515908</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519227</v>
+        <v>518791</v>
       </c>
       <c r="R2" t="n">
-        <v>7056195</v>
+        <v>7056375</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,31 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516432</v>
+        <v>122514876</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,44 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519181</v>
+        <v>519221</v>
       </c>
       <c r="R3" t="n">
-        <v>7056245</v>
+        <v>7056184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,11 +865,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,31 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -944,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515980</v>
+        <v>122516358</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,32 +905,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519364</v>
+        <v>519177</v>
       </c>
       <c r="R4" t="n">
-        <v>7056189</v>
+        <v>7056244</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515908</v>
+        <v>122515545</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518791</v>
+        <v>519292</v>
       </c>
       <c r="R5" t="n">
-        <v>7056375</v>
+        <v>7056181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1169,11 +1099,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1182,6 +1107,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1198,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122516358</v>
+        <v>122516799</v>
       </c>
       <c r="B6" t="n">
         <v>90851</v>
@@ -1243,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519177</v>
+        <v>519073</v>
       </c>
       <c r="R6" t="n">
-        <v>7056244</v>
+        <v>7056218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1330,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515359</v>
+        <v>122515980</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1366,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1380,13 +1330,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519258</v>
+        <v>519364</v>
       </c>
       <c r="R7" t="n">
-        <v>7056164</v>
+        <v>7056189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1420,7 +1370,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,12 +1399,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1472,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122516490</v>
+        <v>122515626</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1488,34 +1438,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519147</v>
+        <v>518946</v>
       </c>
       <c r="R8" t="n">
-        <v>7056252</v>
+        <v>7056283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,31 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1604,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122515717</v>
+        <v>122516490</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1620,39 +1550,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519373</v>
+        <v>519147</v>
       </c>
       <c r="R9" t="n">
-        <v>7056175</v>
+        <v>7056252</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1614,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,12 +1643,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1741,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122514876</v>
+        <v>122516142</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1757,21 +1682,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1781,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519221</v>
+        <v>519227</v>
       </c>
       <c r="R10" t="n">
-        <v>7056184</v>
+        <v>7056195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,6 +1752,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1843,10 +1793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516799</v>
+        <v>122515359</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1859,27 +1809,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1888,10 +1843,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519073</v>
+        <v>519258</v>
       </c>
       <c r="R11" t="n">
-        <v>7056218</v>
+        <v>7056164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1926,6 +1881,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1952,12 +1912,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515626</v>
+        <v>122515390</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1991,39 +1951,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518946</v>
+        <v>519241</v>
       </c>
       <c r="R12" t="n">
-        <v>7056283</v>
+        <v>7056163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2058,11 +2013,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2071,6 +2021,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2087,10 +2062,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515545</v>
+        <v>122515717</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2103,34 +2078,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519292</v>
+        <v>519373</v>
       </c>
       <c r="R13" t="n">
-        <v>7056181</v>
+        <v>7056175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,6 +2145,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2191,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2214,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515390</v>
+        <v>122516432</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,34 +2215,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519241</v>
+        <v>519181</v>
       </c>
       <c r="R14" t="n">
-        <v>7056163</v>
+        <v>7056245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,6 +2287,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515908</v>
+        <v>122515717</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518791</v>
+        <v>519373</v>
       </c>
       <c r="R2" t="n">
-        <v>7056375</v>
+        <v>7056175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514876</v>
+        <v>122515545</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +828,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519221</v>
+        <v>519292</v>
       </c>
       <c r="R3" t="n">
-        <v>7056184</v>
+        <v>7056181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122516358</v>
+        <v>122515390</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +955,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519177</v>
+        <v>519241</v>
       </c>
       <c r="R4" t="n">
-        <v>7056244</v>
+        <v>7056163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1021,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515545</v>
+        <v>122514876</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1082,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519292</v>
+        <v>519221</v>
       </c>
       <c r="R5" t="n">
-        <v>7056181</v>
+        <v>7056184</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,31 +1152,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122516799</v>
+        <v>122515626</v>
       </c>
       <c r="B6" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,27 +1184,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519073</v>
+        <v>518946</v>
       </c>
       <c r="R6" t="n">
-        <v>7056218</v>
+        <v>7056283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1251,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,31 +1264,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515980</v>
+        <v>122516358</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,32 +1296,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,13 +1325,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519364</v>
+        <v>519177</v>
       </c>
       <c r="R7" t="n">
-        <v>7056189</v>
+        <v>7056244</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,11 +1361,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122515626</v>
+        <v>122516490</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,39 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518946</v>
+        <v>519147</v>
       </c>
       <c r="R8" t="n">
-        <v>7056283</v>
+        <v>7056252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1503,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122516490</v>
+        <v>122516142</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,10 +1584,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519147</v>
+        <v>519227</v>
       </c>
       <c r="R9" t="n">
-        <v>7056252</v>
+        <v>7056195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,11 +1620,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122516142</v>
+        <v>122515980</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,37 +1687,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519227</v>
+        <v>519364</v>
       </c>
       <c r="R10" t="n">
-        <v>7056195</v>
+        <v>7056189</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,6 +1759,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1770,12 +1790,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1793,10 +1813,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515359</v>
+        <v>122515908</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1829,12 +1849,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1843,10 +1858,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519258</v>
+        <v>518791</v>
       </c>
       <c r="R11" t="n">
-        <v>7056164</v>
+        <v>7056375</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1883,7 +1898,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,31 +1909,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1935,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515390</v>
+        <v>122516799</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,34 +1941,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519241</v>
+        <v>519073</v>
       </c>
       <c r="R12" t="n">
-        <v>7056163</v>
+        <v>7056218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2039,12 +2034,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2062,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515717</v>
+        <v>122516432</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,16 +2096,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519373</v>
+        <v>519181</v>
       </c>
       <c r="R13" t="n">
-        <v>7056175</v>
+        <v>7056245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516432</v>
+        <v>122515359</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,16 +2215,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2235,7 +2235,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519181</v>
+        <v>519258</v>
       </c>
       <c r="R14" t="n">
-        <v>7056245</v>
+        <v>7056164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2344,7 +2344,7 @@
         <v>122516661</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515717</v>
+        <v>122516799</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519373</v>
+        <v>519073</v>
       </c>
       <c r="R2" t="n">
-        <v>7056175</v>
+        <v>7056218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +758,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -789,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515545</v>
+        <v>122516142</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -852,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519292</v>
+        <v>519227</v>
       </c>
       <c r="R3" t="n">
-        <v>7056181</v>
+        <v>7056195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,12 +911,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515390</v>
+        <v>122516432</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,34 +950,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519241</v>
+        <v>519181</v>
       </c>
       <c r="R4" t="n">
-        <v>7056163</v>
+        <v>7056245</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1022,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122514876</v>
+        <v>122515626</v>
       </c>
       <c r="B5" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,34 +1092,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519221</v>
+        <v>518946</v>
       </c>
       <c r="R5" t="n">
-        <v>7056184</v>
+        <v>7056283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,6 +1157,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1188,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515626</v>
+        <v>122515980</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1207,19 +1227,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518946</v>
+        <v>519364</v>
       </c>
       <c r="R6" t="n">
-        <v>7056283</v>
+        <v>7056189</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,6 +1289,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122516358</v>
+        <v>122515717</v>
       </c>
       <c r="B7" t="n">
-        <v>90852</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,27 +1346,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519177</v>
+        <v>519373</v>
       </c>
       <c r="R7" t="n">
-        <v>7056244</v>
+        <v>7056175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,6 +1413,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,12 +1444,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122516490</v>
+        <v>122515908</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,34 +1483,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519147</v>
+        <v>518791</v>
       </c>
       <c r="R8" t="n">
-        <v>7056252</v>
+        <v>7056375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1552,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,31 +1563,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,10 +1579,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122516142</v>
+        <v>122515545</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519227</v>
+        <v>519292</v>
       </c>
       <c r="R9" t="n">
-        <v>7056195</v>
+        <v>7056181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,12 +1683,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,10 +1706,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515980</v>
+        <v>122514876</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,47 +1722,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519364</v>
+        <v>519221</v>
       </c>
       <c r="R10" t="n">
-        <v>7056189</v>
+        <v>7056184</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,11 +1784,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1772,31 +1792,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1813,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515908</v>
+        <v>122516358</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1829,27 +1824,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1858,10 +1853,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518791</v>
+        <v>519177</v>
       </c>
       <c r="R11" t="n">
-        <v>7056375</v>
+        <v>7056244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1896,11 +1891,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1909,6 +1899,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1925,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122516799</v>
+        <v>122515359</v>
       </c>
       <c r="B12" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,27 +1956,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1970,10 +1990,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519073</v>
+        <v>519258</v>
       </c>
       <c r="R12" t="n">
-        <v>7056218</v>
+        <v>7056164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,6 +2028,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2034,12 +2059,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +2082,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122516432</v>
+        <v>122516490</v>
       </c>
       <c r="B13" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2073,44 +2098,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519181</v>
+        <v>519147</v>
       </c>
       <c r="R13" t="n">
-        <v>7056245</v>
+        <v>7056252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2147,7 +2162,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,12 +2191,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2199,10 +2214,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515359</v>
+        <v>122515390</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,44 +2230,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519258</v>
+        <v>519241</v>
       </c>
       <c r="R14" t="n">
-        <v>7056164</v>
+        <v>7056163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,11 +2292,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122516799</v>
+        <v>122515908</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519073</v>
+        <v>518791</v>
       </c>
       <c r="R2" t="n">
-        <v>7056218</v>
+        <v>7056375</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +758,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,31 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -807,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516142</v>
+        <v>122516358</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519227</v>
+        <v>519177</v>
       </c>
       <c r="R3" t="n">
-        <v>7056195</v>
+        <v>7056244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,12 +896,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122516432</v>
+        <v>122515626</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -973,21 +958,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519181</v>
+        <v>518946</v>
       </c>
       <c r="R4" t="n">
-        <v>7056245</v>
+        <v>7056283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,31 +1015,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1076,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515626</v>
+        <v>122515359</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1112,7 +1067,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1121,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518946</v>
+        <v>519258</v>
       </c>
       <c r="R5" t="n">
-        <v>7056283</v>
+        <v>7056164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,6 +1132,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1188,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515980</v>
+        <v>122515545</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,47 +1189,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519364</v>
+        <v>519292</v>
       </c>
       <c r="R6" t="n">
-        <v>7056189</v>
+        <v>7056181</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,11 +1251,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,12 +1277,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515717</v>
+        <v>122516490</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,39 +1316,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519373</v>
+        <v>519147</v>
       </c>
       <c r="R7" t="n">
-        <v>7056175</v>
+        <v>7056252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,12 +1409,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122515908</v>
+        <v>122516799</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,27 +1448,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1512,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518791</v>
+        <v>519073</v>
       </c>
       <c r="R8" t="n">
-        <v>7056375</v>
+        <v>7056218</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,11 +1515,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1563,6 +1523,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1579,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122515545</v>
+        <v>122514876</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,21 +1580,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1619,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519292</v>
+        <v>519221</v>
       </c>
       <c r="R9" t="n">
-        <v>7056181</v>
+        <v>7056184</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,31 +1650,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1706,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122514876</v>
+        <v>122516142</v>
       </c>
       <c r="B10" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1722,21 +1682,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1746,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519221</v>
+        <v>519227</v>
       </c>
       <c r="R10" t="n">
-        <v>7056184</v>
+        <v>7056195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1792,6 +1752,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1808,10 +1793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516358</v>
+        <v>122515717</v>
       </c>
       <c r="B11" t="n">
-        <v>90855</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,27 +1809,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1853,10 +1838,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519177</v>
+        <v>519373</v>
       </c>
       <c r="R11" t="n">
-        <v>7056244</v>
+        <v>7056175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,6 +1876,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1917,12 +1907,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1940,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515359</v>
+        <v>122516432</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1956,16 +1946,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1976,7 +1966,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1990,10 +1980,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519258</v>
+        <v>519181</v>
       </c>
       <c r="R12" t="n">
-        <v>7056164</v>
+        <v>7056245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2030,7 +2020,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2059,12 +2049,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2082,7 +2072,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122516490</v>
+        <v>122515390</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -2122,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519147</v>
+        <v>519241</v>
       </c>
       <c r="R13" t="n">
-        <v>7056252</v>
+        <v>7056163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,11 +2148,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515390</v>
+        <v>122515980</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,37 +2215,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519241</v>
+        <v>519364</v>
       </c>
       <c r="R14" t="n">
-        <v>7056163</v>
+        <v>7056189</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2292,6 +2287,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515545</v>
+        <v>122515359</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,34 +1804,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519292</v>
+        <v>519258</v>
       </c>
       <c r="R11" t="n">
-        <v>7056181</v>
+        <v>7056164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1866,6 +1876,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1892,12 +1907,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1915,7 +1930,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515359</v>
+        <v>122515980</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1951,7 +1966,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1965,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519258</v>
+        <v>519364</v>
       </c>
       <c r="R12" t="n">
-        <v>7056164</v>
+        <v>7056189</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2005,7 +2020,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2034,12 +2049,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +2072,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515980</v>
+        <v>122515545</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2073,47 +2088,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519364</v>
+        <v>519292</v>
       </c>
       <c r="R13" t="n">
-        <v>7056189</v>
+        <v>7056181</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,11 +2150,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515359</v>
+        <v>122515545</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,44 +1804,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519258</v>
+        <v>519292</v>
       </c>
       <c r="R11" t="n">
-        <v>7056164</v>
+        <v>7056181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,11 +1866,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1907,12 +1892,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1930,7 +1915,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515980</v>
+        <v>122515359</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1966,7 +1951,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1980,13 +1965,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519364</v>
+        <v>519258</v>
       </c>
       <c r="R12" t="n">
-        <v>7056189</v>
+        <v>7056164</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2020,7 +2005,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,12 +2034,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2072,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515545</v>
+        <v>122515980</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2088,37 +2073,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519292</v>
+        <v>519364</v>
       </c>
       <c r="R13" t="n">
-        <v>7056181</v>
+        <v>7056189</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,6 +2145,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122516358</v>
+        <v>122516432</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519177</v>
+        <v>519181</v>
       </c>
       <c r="R2" t="n">
-        <v>7056244</v>
+        <v>7056245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +820,7 @@
         <v>122516490</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122516799</v>
+        <v>122515980</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,27 +965,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519073</v>
+        <v>519364</v>
       </c>
       <c r="R4" t="n">
-        <v>7056218</v>
+        <v>7056189</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,6 +1035,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1091,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515626</v>
+        <v>122515359</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1107,7 +1127,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1116,10 +1141,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518946</v>
+        <v>519258</v>
       </c>
       <c r="R5" t="n">
-        <v>7056283</v>
+        <v>7056164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,7 +1181,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,6 +1192,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122515908</v>
+        <v>122516799</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,27 +1249,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1228,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518791</v>
+        <v>519073</v>
       </c>
       <c r="R6" t="n">
-        <v>7056375</v>
+        <v>7056218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,11 +1316,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1279,6 +1324,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515717</v>
+        <v>122516142</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,39 +1381,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519373</v>
+        <v>519227</v>
       </c>
       <c r="R7" t="n">
-        <v>7056175</v>
+        <v>7056195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,11 +1443,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1409,12 +1469,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1432,10 +1492,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514876</v>
+        <v>122516358</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,16 +1526,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519221</v>
+        <v>519177</v>
       </c>
       <c r="R8" t="n">
-        <v>7056184</v>
+        <v>7056244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1518,6 +1583,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1537,7 +1627,7 @@
         <v>122515390</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1661,10 +1751,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122516142</v>
+        <v>122515626</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,34 +1767,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519227</v>
+        <v>518946</v>
       </c>
       <c r="R10" t="n">
-        <v>7056195</v>
+        <v>7056283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,6 +1834,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1747,31 +1847,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,7 +1866,7 @@
         <v>122515545</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1915,10 +1990,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515359</v>
+        <v>122514876</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,44 +2006,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519258</v>
+        <v>519221</v>
       </c>
       <c r="R12" t="n">
-        <v>7056164</v>
+        <v>7056184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,11 +2068,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2016,31 +2076,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2057,7 +2092,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515980</v>
+        <v>122515908</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2096,24 +2131,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519364</v>
+        <v>518791</v>
       </c>
       <c r="R13" t="n">
-        <v>7056189</v>
+        <v>7056375</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2147,7 +2177,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,31 +2188,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2199,7 +2204,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122516432</v>
+        <v>122515717</v>
       </c>
       <c r="B14" t="n">
         <v>57494</v>
@@ -2238,21 +2243,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519181</v>
+        <v>519373</v>
       </c>
       <c r="R14" t="n">
-        <v>7056245</v>
+        <v>7056175</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122516432</v>
+        <v>122515390</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519181</v>
+        <v>519241</v>
       </c>
       <c r="R2" t="n">
-        <v>7056245</v>
+        <v>7056163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -794,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516490</v>
+        <v>122516432</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519147</v>
+        <v>519181</v>
       </c>
       <c r="R3" t="n">
-        <v>7056252</v>
+        <v>7056245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Kraftigt hackspår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,7 +944,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515980</v>
+        <v>122515626</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -988,24 +983,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519364</v>
+        <v>518946</v>
       </c>
       <c r="R4" t="n">
-        <v>7056189</v>
+        <v>7056283</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,31 +1040,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1091,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515359</v>
+        <v>122515717</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,16 +1072,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1127,12 +1092,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1141,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519258</v>
+        <v>519373</v>
       </c>
       <c r="R5" t="n">
-        <v>7056164</v>
+        <v>7056175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1181,7 +1141,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack.</t>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1365,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122516142</v>
+        <v>122515908</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,34 +1341,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519227</v>
+        <v>518791</v>
       </c>
       <c r="R7" t="n">
-        <v>7056195</v>
+        <v>7056375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,6 +1408,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1451,31 +1421,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1492,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122516358</v>
+        <v>122515980</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1508,27 +1453,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1537,13 +1487,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519177</v>
+        <v>519364</v>
       </c>
       <c r="R8" t="n">
-        <v>7056244</v>
+        <v>7056189</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1573,6 +1523,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en i övrigt hackspettsbearbetad relativt grov stående döende granstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,10 +1579,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122515390</v>
+        <v>122514876</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1640,21 +1595,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1664,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519241</v>
+        <v>519221</v>
       </c>
       <c r="R9" t="n">
-        <v>7056163</v>
+        <v>7056184</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1710,31 +1665,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1751,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515626</v>
+        <v>122516142</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1767,39 +1697,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518946</v>
+        <v>519227</v>
       </c>
       <c r="R10" t="n">
-        <v>7056283</v>
+        <v>7056195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1834,11 +1759,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1847,6 +1767,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1863,7 +1808,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122515545</v>
+        <v>122516490</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1903,10 +1848,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519292</v>
+        <v>519147</v>
       </c>
       <c r="R11" t="n">
-        <v>7056181</v>
+        <v>7056252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1941,6 +1886,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1967,12 +1917,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1990,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122514876</v>
+        <v>122515359</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2006,34 +1956,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519221</v>
+        <v>519258</v>
       </c>
       <c r="R12" t="n">
-        <v>7056184</v>
+        <v>7056164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2068,6 +2028,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2076,6 +2041,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2092,10 +2082,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122515908</v>
+        <v>122516358</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2108,27 +2098,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2137,10 +2127,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518791</v>
+        <v>519177</v>
       </c>
       <c r="R13" t="n">
-        <v>7056375</v>
+        <v>7056244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2175,11 +2165,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2173,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2204,10 +2214,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515717</v>
+        <v>122515545</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2220,39 +2230,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519373</v>
+        <v>519292</v>
       </c>
       <c r="R14" t="n">
-        <v>7056175</v>
+        <v>7056181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,11 +2292,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122515390</v>
+        <v>122515626</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519241</v>
+        <v>518946</v>
       </c>
       <c r="R2" t="n">
-        <v>7056163</v>
+        <v>7056283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,31 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122516432</v>
+        <v>122515908</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,21 +826,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519181</v>
+        <v>518791</v>
       </c>
       <c r="R3" t="n">
-        <v>7056245</v>
+        <v>7056375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kraftigt hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,31 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -944,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515626</v>
+        <v>122516490</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518946</v>
+        <v>519147</v>
       </c>
       <c r="R4" t="n">
-        <v>7056283</v>
+        <v>7056252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +990,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515717</v>
+        <v>122516142</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519373</v>
+        <v>519227</v>
       </c>
       <c r="R5" t="n">
-        <v>7056175</v>
+        <v>7056195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,11 +1109,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,12 +1135,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122516799</v>
+        <v>122514876</v>
       </c>
       <c r="B6" t="n">
         <v>90962</v>
@@ -1227,21 +1192,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519073</v>
+        <v>519221</v>
       </c>
       <c r="R6" t="n">
-        <v>7056218</v>
+        <v>7056184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,31 +1244,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1325,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122515908</v>
+        <v>122516799</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,27 +1276,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1370,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518791</v>
+        <v>519073</v>
       </c>
       <c r="R7" t="n">
-        <v>7056375</v>
+        <v>7056218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1343,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1421,6 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1579,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122514876</v>
+        <v>122516432</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,34 +1550,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519221</v>
+        <v>519181</v>
       </c>
       <c r="R9" t="n">
-        <v>7056184</v>
+        <v>7056245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1657,6 +1622,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1665,6 +1635,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1681,7 +1676,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122516142</v>
+        <v>122515545</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1721,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519227</v>
+        <v>519292</v>
       </c>
       <c r="R10" t="n">
-        <v>7056195</v>
+        <v>7056181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,12 +1780,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1808,7 +1803,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122516490</v>
+        <v>122515390</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1848,10 +1843,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519147</v>
+        <v>519241</v>
       </c>
       <c r="R11" t="n">
-        <v>7056252</v>
+        <v>7056163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,11 +1879,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122515359</v>
+        <v>122516358</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1956,32 +1946,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1990,10 +1975,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519258</v>
+        <v>519177</v>
       </c>
       <c r="R12" t="n">
-        <v>7056164</v>
+        <v>7056244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2028,11 +2013,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2059,12 +2039,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2082,10 +2062,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122516358</v>
+        <v>122515717</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2098,27 +2078,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2127,10 +2107,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519177</v>
+        <v>519373</v>
       </c>
       <c r="R13" t="n">
-        <v>7056244</v>
+        <v>7056175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,6 +2145,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen av en döende rätt så grov gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2191,12 +2176,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2214,10 +2199,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122515545</v>
+        <v>122515359</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,34 +2215,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519292</v>
+        <v>519258</v>
       </c>
       <c r="R14" t="n">
-        <v>7056181</v>
+        <v>7056164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,6 +2287,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60198-2024 artfynd.xlsx
+++ b/artfynd/A 60198-2024 artfynd.xlsx
@@ -1534,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122516432</v>
+        <v>122515545</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,44 +1550,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519181</v>
+        <v>519292</v>
       </c>
       <c r="R9" t="n">
-        <v>7056245</v>
+        <v>7056181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1622,11 +1612,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kraftigt hackspår.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1653,12 +1638,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1676,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122515545</v>
+        <v>122516432</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,34 +1677,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjån, Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519292</v>
+        <v>519181</v>
       </c>
       <c r="R10" t="n">
-        <v>7056181</v>
+        <v>7056245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,6 +1749,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kraftigt hackspår.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
